--- a/03_Outputs/Bioenergetica_Norte/10_Seguridad/seguridad.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/10_Seguridad/seguridad.xlsx
@@ -19,6 +19,11 @@
     <sheet name="P6_cambio_municipio" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="irv" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="desaparecidos" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="_fig_01" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="_fig_02" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="_fig_03" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="_fig_04" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="_fig_05" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
 </workbook>
 </file>
@@ -2189,6 +2194,1161 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>periodo</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ambito</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>n_resp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2018</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0.247309549143037</v>
+      </c>
+      <c r="D2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2019 (1)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0.181036257130808</v>
+      </c>
+      <c r="D3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2019 (2)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0.145889472818591</v>
+      </c>
+      <c r="D4">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0.186356719168937</v>
+      </c>
+      <c r="D5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2022</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0.148855733765853</v>
+      </c>
+      <c r="D6">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2023</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0.157717210185655</v>
+      </c>
+      <c r="D7">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0.155654086292368</v>
+      </c>
+      <c r="D8">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0.10353955335921</v>
+      </c>
+      <c r="D9">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0.360135034744621</v>
+      </c>
+      <c r="D10">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2019 (1)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0.251598090378401</v>
+      </c>
+      <c r="D11">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2019 (2)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0.208759158077822</v>
+      </c>
+      <c r="D12">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0.253178411584232</v>
+      </c>
+      <c r="D13">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0.160979631898894</v>
+      </c>
+      <c r="D14">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0.230572694316667</v>
+      </c>
+      <c r="D15">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0.23923886999938</v>
+      </c>
+      <c r="D16">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0.208948079783054</v>
+      </c>
+      <c r="D17">
+        <v>249</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>n_solicitudes</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>pob</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>tasa_solicitudes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>58</v>
+      </c>
+      <c r="C2">
+        <v>12511</v>
+      </c>
+      <c r="D2">
+        <v>4.63592039005675</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>159</v>
+      </c>
+      <c r="C3">
+        <v>21035</v>
+      </c>
+      <c r="D3">
+        <v>7.55883052056097</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>117</v>
+      </c>
+      <c r="C4">
+        <v>7957</v>
+      </c>
+      <c r="D4">
+        <v>14.7040341837376</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>45</v>
+      </c>
+      <c r="C5">
+        <v>10005</v>
+      </c>
+      <c r="D5">
+        <v>4.49775112443778</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3942</v>
+      </c>
+      <c r="D6">
+        <v>1.01471334348047</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>7009</v>
+      </c>
+      <c r="D7">
+        <v>1.85475816806962</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>10373</v>
+      </c>
+      <c r="D8">
+        <v>2.60291140460812</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>445</v>
+      </c>
+      <c r="C9">
+        <v>29515</v>
+      </c>
+      <c r="D9">
+        <v>15.0770794511265</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>80</v>
+      </c>
+      <c r="C10">
+        <v>7402</v>
+      </c>
+      <c r="D10">
+        <v>10.8078897595245</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>4017</v>
+      </c>
+      <c r="D11">
+        <v>0.497883993029624</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>41</v>
+      </c>
+      <c r="C12">
+        <v>4824</v>
+      </c>
+      <c r="D12">
+        <v>8.49917081260365</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>155</v>
+      </c>
+      <c r="C13">
+        <v>15014</v>
+      </c>
+      <c r="D13">
+        <v>10.3236978819768</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>120</v>
+      </c>
+      <c r="C14">
+        <v>41884</v>
+      </c>
+      <c r="D14">
+        <v>2.86505586858944</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>desaparecidos</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>prop_desaparecidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>517</v>
+      </c>
+      <c r="C2">
+        <v>0.362298528381219</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>265</v>
+      </c>
+      <c r="C3">
+        <v>0.185704274702172</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>161</v>
+      </c>
+      <c r="C4">
+        <v>0.112824106517169</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>158</v>
+      </c>
+      <c r="C5">
+        <v>0.110721793973371</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>65</v>
+      </c>
+      <c r="C6">
+        <v>0.0455501051156272</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>0.0427470217238963</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>0.0294323756131745</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>38</v>
+      </c>
+      <c r="C9">
+        <v>0.0266292922214436</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>0.0245269796776454</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>0.02312543798178</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>21</v>
+      </c>
+      <c r="C12">
+        <v>0.0147161878065872</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>0.0112123335669236</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>15</v>
+      </c>
+      <c r="C14">
+        <v>0.0105115627189909</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>victimas_ocurrencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>6757</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>23517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>18213</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>8670</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>57522</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>7404</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>7292</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>25760</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>19298</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>hecho</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>victimas_ocurrencia</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>proporcion_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Desplazamiento forzado</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>130639</v>
+      </c>
+      <c r="C2">
+        <v>0.71853497824688</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Homicidio</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>19499</v>
+      </c>
+      <c r="C3">
+        <v>0.107247556555362</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Amenaza</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>19023</v>
+      </c>
+      <c r="C4">
+        <v>0.104629481940235</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Desaparición forzada</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>3194</v>
+      </c>
+      <c r="C5">
+        <v>0.0175675006737692</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pérdida de bienes muebles/inmuebles</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2015</v>
+      </c>
+      <c r="C6">
+        <v>0.011082815860252</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Confinamiento</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1554</v>
+      </c>
+      <c r="C7">
+        <v>0.0085472435964425</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Acto terrorista/atentados/combates</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1523</v>
+      </c>
+      <c r="C8">
+        <v>0.00837673873705401</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>1031</v>
+      </c>
+      <c r="C9">
+        <v>0.005670661613856</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Minas antipersonal/MUSE</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>872</v>
+      </c>
+      <c r="C10">
+        <v>0.00479613668989566</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Secuestro</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>818</v>
+      </c>
+      <c r="C11">
+        <v>0.00449912822515442</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lesiones personales físicas</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>684</v>
+      </c>
+      <c r="C12">
+        <v>0.00376210722005577</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Delitos contra libertad/integridad sexual</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>408</v>
+      </c>
+      <c r="C13">
+        <v>0.00224406395582274</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vinculación de NNA a grupos armados</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>224</v>
+      </c>
+      <c r="C14">
+        <v>0.00123203511300072</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lesiones personales psicológicas</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>195</v>
+      </c>
+      <c r="C15">
+        <v>0.00107253056712116</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tortura</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>117</v>
+      </c>
+      <c r="C16">
+        <v>0.000643518340272698</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Abandono o despojo de tierras</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>0.0000935026648259475</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:I18"/>
